--- a/data/trans_dic/IP12B$alergia-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,37</t>
+          <t>0,0; 36,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,93</t>
+          <t>0,0; 18,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,98</t>
+          <t>0,0; 16,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,51</t>
+          <t>0,0; 13,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,84</t>
+          <t>0,0; 16,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,33</t>
+          <t>0,0; 13,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 14,31</t>
+          <t>1,39; 14,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,84; 16,3</t>
+          <t>1,82; 15,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,55</t>
+          <t>1,05; 10,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,73; 10,94</t>
+          <t>1,91; 10,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 12,42</t>
+          <t>2,82; 13,24</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,9</t>
+          <t>0,0; 31,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 7,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,98; 32,73</t>
+          <t>2,97; 32,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,49</t>
+          <t>0,0; 26,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,36</t>
+          <t>0,0; 42,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,55</t>
+          <t>0,0; 22,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,43</t>
+          <t>0,0; 18,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 22,03</t>
+          <t>1,95; 20,83</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,21</t>
+          <t>1,45; 12,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 8,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 15,18</t>
+          <t>2,37; 14,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 12,06</t>
+          <t>1,27; 10,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,62; 14,95</t>
+          <t>2,35; 14,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 13,14</t>
+          <t>1,4; 12,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,9</t>
+          <t>1,59; 8,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 9,4</t>
+          <t>2,03; 9,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,88; 11,19</t>
+          <t>2,82; 11,34</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2584</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3244</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1571</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2660</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>4077</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4183</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4966</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4803</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 5290</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4199</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>631; 6761</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>661; 5809</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>640; 6237</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1535; 8566</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1925; 9029</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>696</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1345</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2047</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2745</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>497; 5435</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2622</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4800</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4094</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4935</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>506; 5409</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1570</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3618</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>4005</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5757</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>6230</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>637; 5594</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5009</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7851</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>592; 5107</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1492; 9129</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>669; 6180</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>1438; 8142</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2532; 11980</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2904; 11675</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$alergia-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,66</t>
+          <t>0,0; 44,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,96</t>
+          <t>0,0; 15,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,76</t>
+          <t>0,0; 17,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,7</t>
+          <t>0,0; 13,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,63</t>
+          <t>0,0; 15,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,39</t>
+          <t>0,0; 13,83</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 14,93</t>
+          <t>1,38; 14,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 15,97</t>
+          <t>1,8; 16,36</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,05; 10,23</t>
+          <t>1,27; 10,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,91; 10,66</t>
+          <t>1,82; 11,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,82; 13,24</t>
+          <t>2,12; 12,32</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,93</t>
+          <t>0,0; 38,51</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -908,17 +908,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 32,5</t>
+          <t>3,12; 31,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,6</t>
+          <t>0,0; 26,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,79</t>
+          <t>0,0; 38,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,19</t>
+          <t>0,0; 21,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,01</t>
+          <t>0,0; 20,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 20,83</t>
+          <t>1,95; 20,32</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 12,75</t>
+          <t>1,45; 13,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,17</t>
+          <t>0,0; 8,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 14,24</t>
+          <t>1,82; 13,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,93</t>
+          <t>0,0; 9,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,35; 14,36</t>
+          <t>2,46; 15,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 12,91</t>
+          <t>1,37; 13,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,99</t>
+          <t>1,99; 9,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 9,59</t>
+          <t>1,84; 9,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 11,34</t>
+          <t>2,9; 11,42</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por ronchas, picor, alergias (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2584</t>
+          <t>0; 3137</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3244</t>
+          <t>0; 2690</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4966</t>
+          <t>0; 5119</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4803</t>
+          <t>0; 4695</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5290</t>
+          <t>0; 4793</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4199</t>
+          <t>0; 4336</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>631; 6761</t>
+          <t>624; 6349</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>661; 5809</t>
+          <t>653; 5951</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>640; 6237</t>
+          <t>774; 6230</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1535; 8566</t>
+          <t>1465; 8876</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1925; 9029</t>
+          <t>1444; 8398</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2745</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1642,17 +1642,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497; 5435</t>
+          <t>522; 5344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2622</t>
+          <t>0; 2638</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4800</t>
+          <t>0; 4353</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1662,17 +1662,17 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4094</t>
+          <t>0; 4048</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4935</t>
+          <t>0; 5743</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>506; 5409</t>
+          <t>505; 5278</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>637; 5594</t>
+          <t>635; 5891</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5009</t>
+          <t>0; 5198</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1306; 7851</t>
+          <t>1004; 7595</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>592; 5107</t>
+          <t>0; 4541</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1492; 9129</t>
+          <t>1560; 9698</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>669; 6180</t>
+          <t>657; 6443</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1438; 8142</t>
+          <t>1798; 8169</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2532; 11980</t>
+          <t>2299; 11711</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2904; 11675</t>
+          <t>2982; 11763</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$alergia-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$alergia-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -630,22 +630,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -683,24 +683,24 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 40,37</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 44,5</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,72</t>
+          <t>0,0; 15,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,54%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,8%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>4,48%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>0,0; 12,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,4</t>
+          <t>1,38; 14,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,06</t>
+          <t>1,84; 16,3</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,83</t>
+          <t>0,0; 14,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 14,02</t>
+          <t>0,0; 15,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 16,36</t>
+          <t>0,0; 14,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 10,22</t>
+          <t>1,17; 10,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 11,05</t>
+          <t>1,73; 10,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 12,32</t>
+          <t>2,75; 12,42</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,58%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9,37%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>8,1%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>12,24%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,58%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,51</t>
+          <t>0,0; 33,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>0,0; 39,36</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3,12; 31,95</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,77</t>
+          <t>0,0; 31,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,98; 32,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,94</t>
+          <t>0,0; 25,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,96</t>
+          <t>0,0; 18,43</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 20,32</t>
+          <t>1,96; 22,03</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,46%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,83%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2,56%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>6,56%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,59%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>5,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 13,43</t>
+          <t>1,25; 12,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,48</t>
+          <t>2,62; 14,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 13,78</t>
+          <t>1,38; 13,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,72</t>
+          <t>1,45; 13,21</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 15,26</t>
+          <t>0,0; 7,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 13,46</t>
+          <t>2,37; 15,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 9,02</t>
+          <t>1,57; 8,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 9,38</t>
+          <t>2,06; 9,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,9; 11,42</t>
+          <t>2,88; 11,19</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1205,22 +1205,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1311,24 +1311,24 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 2846</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3137</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2690</t>
+          <t>0; 2725</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1368,27 +1368,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2507</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1423</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1570</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1571</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1237</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2507</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 5119</t>
+          <t>0; 3866</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>623; 6482</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 4793</t>
+          <t>669; 5928</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4336</t>
+          <t>0; 4437</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>624; 6349</t>
+          <t>0; 5438</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>653; 5951</t>
+          <t>0; 4723</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>774; 6230</t>
+          <t>711; 6432</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1465; 8876</t>
+          <t>1392; 8787</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1444; 8398</t>
+          <t>1874; 8471</t>
         </is>
       </c>
     </row>
@@ -1531,27 +1531,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>696</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2047</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3311</t>
+          <t>0; 3300</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0; 4415</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>522; 5344</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2638</t>
+          <t>0; 2743</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4353</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>498; 5474</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4048</t>
+          <t>0; 4714</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5743</t>
+          <t>0; 5050</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>505; 5278</t>
+          <t>510; 5723</t>
         </is>
       </c>
     </row>
@@ -1694,27 +1694,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1885</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>4187</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2612</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2120</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>1570</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3618</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1885</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4187</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2612</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>635; 5891</t>
+          <t>586; 5633</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5198</t>
+          <t>1668; 9499</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1004; 7595</t>
+          <t>659; 6287</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4541</t>
+          <t>634; 5796</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1560; 9698</t>
+          <t>0; 4880</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>657; 6443</t>
+          <t>1305; 8368</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1798; 8169</t>
+          <t>1425; 8063</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2299; 11711</t>
+          <t>2571; 11735</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2982; 11763</t>
+          <t>2964; 11520</t>
         </is>
       </c>
     </row>
